--- a/reports/Visualizar/resultados.xlsx
+++ b/reports/Visualizar/resultados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GIT\Case M\reports\Visualizar\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E9E60139-9BE2-4EF7-900D-3B55A0DFCAF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2BF4FC82-44CB-4CD7-A1B4-5E1F1C38A2D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{572BF53C-7B4C-433F-BC03-B23CFC825485}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{4DF1D648-5CC5-478A-9A03-71F4940B0E27}"/>
   </bookViews>
   <sheets>
     <sheet name="resultados" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="4">
   <si>
     <t>nome_teste,descricao,variante_vencedora,decisao,data_analise</t>
   </si>
@@ -891,8 +891,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2CEB26F3-B9C5-402E-9BF1-1EFD5D7DE492}">
-  <dimension ref="A1:A5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F388AB9-93E1-41CD-8B63-B2B93F213C23}">
+  <dimension ref="A1:A8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
@@ -920,6 +920,21 @@
         <v>3</v>
       </c>
     </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
